--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/1904-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/1904-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9286E6CC-F32B-4302-B138-5B3ADA827D1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EFC4F092-6BF4-4EDB-BB32-159F7A9036DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{33760231-35CA-4A38-BE11-38F760C6D3CF}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{88D3DD0D-0F36-4373-8E16-BA503850C7D9}"/>
   </bookViews>
   <sheets>
     <sheet name="1904-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1544,28 +1544,27 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D566F780-9DEA-471C-9182-5F6AF903E571}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B79FD92-F486-462D-9644-9E719911C8F2}">
   <dimension ref="A1:X48"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="10.75" customWidth="1"/>
-    <col min="3" max="3" width="9.75" customWidth="1"/>
-    <col min="4" max="6" width="6" customWidth="1"/>
-    <col min="7" max="7" width="6.25" customWidth="1"/>
-    <col min="8" max="8" width="6" customWidth="1"/>
-    <col min="9" max="10" width="6.25" customWidth="1"/>
-    <col min="11" max="13" width="6" customWidth="1"/>
-    <col min="14" max="15" width="6.25" customWidth="1"/>
-    <col min="16" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="6.25" customWidth="1"/>
-    <col min="20" max="20" width="6" customWidth="1"/>
-    <col min="21" max="21" width="6.25" customWidth="1"/>
-    <col min="22" max="22" width="6" customWidth="1"/>
-    <col min="23" max="23" width="6.25" customWidth="1"/>
-    <col min="24" max="24" width="6.875" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
@@ -1599,7 +1598,7 @@
       <c r="W1" s="29"/>
       <c r="X1" s="21"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="22" t="s">
         <v>1</v>
       </c>
@@ -1635,7 +1634,7 @@
       <c r="W2" s="31"/>
       <c r="X2" s="32"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="22" t="s">
         <v>2</v>
       </c>
@@ -1687,7 +1686,7 @@
       </c>
       <c r="X3" s="35"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="24"/>
       <c r="B4" s="25"/>
       <c r="C4" s="7"/>
@@ -1755,7 +1754,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="36">
         <v>2024</v>
       </c>
@@ -1827,7 +1826,7 @@
         <v>2.92</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="38">
         <v>2023</v>
       </c>
@@ -1899,7 +1898,7 @@
         <v>2.67</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="36">
         <v>2022</v>
       </c>
@@ -1971,7 +1970,7 @@
         <v>4.05</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="38">
         <v>2021</v>
       </c>
@@ -2043,7 +2042,7 @@
         <v>7.57</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="36">
         <v>2020</v>
       </c>
@@ -2115,7 +2114,7 @@
         <v>6.38</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="38">
         <v>2019</v>
       </c>
@@ -2187,7 +2186,7 @@
         <v>6.84</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="36">
         <v>2018</v>
       </c>
@@ -2259,7 +2258,7 @@
         <v>6.36</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="38">
         <v>2017</v>
       </c>
@@ -2331,7 +2330,7 @@
         <v>4.6500000000000004</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="36">
         <v>2016</v>
       </c>
@@ -2403,7 +2402,7 @@
         <v>3.85</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="38">
         <v>2015</v>
       </c>
@@ -2475,7 +2474,7 @@
         <v>5.58</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="36">
         <v>2014</v>
       </c>
@@ -2547,7 +2546,7 @@
         <v>3.48</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="38">
         <v>2013</v>
       </c>
@@ -2619,7 +2618,7 @@
         <v>4.9000000000000004</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="36">
         <v>2012</v>
       </c>
@@ -2691,7 +2690,7 @@
         <v>4.92</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="38">
         <v>2011</v>
       </c>
@@ -2763,7 +2762,7 @@
         <v>2.86</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="36">
         <v>2010</v>
       </c>
@@ -2835,7 +2834,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="38">
         <v>2009</v>
       </c>
@@ -2907,7 +2906,7 @@
         <v>6.54</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="36">
         <v>2008</v>
       </c>
@@ -2979,7 +2978,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="38">
         <v>2007</v>
       </c>
@@ -3051,7 +3050,7 @@
         <v>7.26</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="36">
         <v>2006</v>
       </c>
@@ -3123,7 +3122,7 @@
         <v>7.04</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="38">
         <v>2005</v>
       </c>
@@ -3195,7 +3194,7 @@
         <v>6.46</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="36">
         <v>2004</v>
       </c>
@@ -3267,7 +3266,7 @@
         <v>9.33</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="38">
         <v>2003</v>
       </c>
@@ -3339,7 +3338,7 @@
         <v>6.03</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="36">
         <v>2002</v>
       </c>
@@ -3411,7 +3410,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="38">
         <v>2001</v>
       </c>
@@ -3483,7 +3482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="40">
         <v>2000</v>
       </c>
@@ -3555,7 +3554,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="42"/>
       <c r="B30" s="43"/>
       <c r="C30" s="18" t="s">
@@ -3583,7 +3582,7 @@
       <c r="W30" s="49"/>
       <c r="X30" s="45"/>
     </row>
-    <row r="31" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="38">
         <v>1999</v>
       </c>
@@ -3655,7 +3654,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="36">
         <v>1998</v>
       </c>
@@ -3727,7 +3726,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="38">
         <v>1997</v>
       </c>
@@ -3799,7 +3798,7 @@
         <v>4.95</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="36">
         <v>1996</v>
       </c>
@@ -3871,7 +3870,7 @@
         <v>3.29</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="38">
         <v>1995</v>
       </c>
@@ -3943,7 +3942,7 @@
         <v>5.56</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="36">
         <v>1994</v>
       </c>
@@ -4015,7 +4014,7 @@
         <v>10.8</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="38">
         <v>1993</v>
       </c>
@@ -4087,7 +4086,7 @@
         <v>3.33</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="36">
         <v>1992</v>
       </c>
@@ -4159,7 +4158,7 @@
         <v>1.43</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="38">
         <v>1991</v>
       </c>
@@ -4231,7 +4230,7 @@
         <v>5.16</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="36">
         <v>1990</v>
       </c>
@@ -4303,7 +4302,7 @@
         <v>3.31</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="38">
         <v>1989</v>
       </c>
@@ -4375,7 +4374,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="36">
         <v>1988</v>
       </c>
@@ -4447,7 +4446,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="38">
         <v>1987</v>
       </c>
@@ -4519,7 +4518,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="44" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="36">
         <v>1986</v>
       </c>
@@ -4591,7 +4590,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="45" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A45" s="38">
         <v>1985</v>
       </c>
@@ -4663,7 +4662,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="46" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A46" s="36">
         <v>1984</v>
       </c>
@@ -4735,7 +4734,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="47" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A47" s="38">
         <v>1983</v>
       </c>
@@ -4807,7 +4806,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="48" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A48" s="36" t="s">
         <v>61</v>
       </c>
